--- a/nonprofit_employee_forms/005_nonprofit_employee_burnout_study--nonprofit_employee_forms.xlsx
+++ b/nonprofit_employee_forms/005_nonprofit_employee_burnout_study--nonprofit_employee_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Does your organization have a burnout prevention and management plan</t>
+          <t>Burnout Prevention And Management Plan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How often do you experience burnout</t>
+          <t>Burnout Frequency Rating</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>burnout_impact_rating</t>
+          <t>burnout_impact_rating_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>burnout_prevention_and_management_plan_rating</t>
+          <t>burnout_prevention_and_management_plan_rating_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How effective is burnout prevention and management plan</t>
+          <t>Burnout Prevention And Management Plan Rating 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2696,7 +2696,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>burnout_impact_rating_choices</t>
+          <t>burnout_impact_rating_2_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2713,7 +2713,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>burnout_impact_rating_choices</t>
+          <t>burnout_impact_rating_2_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2730,7 +2730,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>burnout_impact_rating_choices</t>
+          <t>burnout_impact_rating_2_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2747,7 +2747,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>burnout_impact_rating_choices</t>
+          <t>burnout_impact_rating_2_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2764,7 +2764,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>burnout_impact_rating_choices</t>
+          <t>burnout_impact_rating_2_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2866,7 +2866,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>burnout_prevention_and_management_plan_rating_choices</t>
+          <t>burnout_prevention_and_management_plan_rating_2_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2883,7 +2883,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>burnout_prevention_and_management_plan_rating_choices</t>
+          <t>burnout_prevention_and_management_plan_rating_2_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2900,7 +2900,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>burnout_prevention_and_management_plan_rating_choices</t>
+          <t>burnout_prevention_and_management_plan_rating_2_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2917,7 +2917,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>burnout_prevention_and_management_plan_rating_choices</t>
+          <t>burnout_prevention_and_management_plan_rating_2_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>burnout_prevention_and_management_plan_rating_choices</t>
+          <t>burnout_prevention_and_management_plan_rating_2_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
